--- a/exports/sobreaviso/folha_ponto_sobreaviso_Edinei_Rocha_20260721_20260820.xlsx
+++ b/exports/sobreaviso/folha_ponto_sobreaviso_Edinei_Rocha_20260721_20260820.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Edinei Rocha</t>
+          <t>Edinei Rocha</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>USR-2</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Manutencao</t>
+          <t>Operacao</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1173,18 +1173,18 @@
       <c r="J20" s="4" t="inlineStr"/>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr"/>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>21:00</t>
         </is>
       </c>
     </row>
@@ -1219,18 +1219,18 @@
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr"/>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -1645,26 +1645,18 @@
           <t>0:00</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr"/>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>24:00</t>
-        </is>
-      </c>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>7:00</t>
-        </is>
-      </c>
-      <c r="M32" s="6" t="inlineStr"/>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="n"/>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>7:00</t>
+          <t>0:00</t>
         </is>
       </c>
     </row>
@@ -1691,26 +1683,18 @@
           <t>0:00</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr"/>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>24:00</t>
-        </is>
-      </c>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>24:00</t>
-        </is>
-      </c>
-      <c r="M33" s="6" t="inlineStr"/>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="n"/>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>0:00</t>
         </is>
       </c>
     </row>
@@ -1737,26 +1721,18 @@
           <t>0:00</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr"/>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>24:00</t>
-        </is>
-      </c>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="4" t="n"/>
+      <c r="K34" s="4" t="n"/>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>24:00</t>
-        </is>
-      </c>
-      <c r="M34" s="6" t="inlineStr"/>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="n"/>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>0:00</t>
         </is>
       </c>
     </row>
@@ -1783,26 +1759,18 @@
           <t>0:00</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr"/>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>24:00</t>
-        </is>
-      </c>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n"/>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>24:00</t>
-        </is>
-      </c>
-      <c r="M35" s="6" t="inlineStr"/>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="n"/>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>0:00</t>
         </is>
       </c>
     </row>
@@ -1829,26 +1797,18 @@
           <t>0:00</t>
         </is>
       </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr"/>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
+      <c r="I36" s="4" t="n"/>
+      <c r="J36" s="4" t="n"/>
+      <c r="K36" s="4" t="n"/>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>7:00</t>
-        </is>
-      </c>
-      <c r="M36" s="6" t="inlineStr"/>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="n"/>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>7:00</t>
+          <t>0:00</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1946,7 @@
       <c r="M40" s="7" t="n"/>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>149:00</t>
+          <t>56:00</t>
         </is>
       </c>
     </row>
